--- a/data/trans_orig/IP17-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51531</t>
+          <t>51043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49274</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71893</t>
+          <t>72605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95020</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54640</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70633</t>
+          <t>71010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72106</t>
+          <t>73117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88883</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132531</t>
+          <t>132914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155658</t>
+          <t>154946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39637</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60085</t>
+          <t>60535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50584</t>
+          <t>50392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72754</t>
+          <t>72588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97628</t>
+          <t>96017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127921</t>
+          <t>126193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193120</t>
+          <t>192670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213568</t>
+          <t>213764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>181002</t>
+          <t>181168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203172</t>
+          <t>203364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379040</t>
+          <t>380768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409333</t>
+          <t>410944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27030</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36641</t>
+          <t>35289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>37269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58453</t>
+          <t>57180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100518</t>
+          <t>99855</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113671</t>
+          <t>113107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104874</t>
+          <t>106226</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120949</t>
+          <t>120700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210610</t>
+          <t>211883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231363</t>
+          <t>231794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27781</t>
+          <t>27343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42554</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42752</t>
+          <t>43581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64221</t>
+          <t>65547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166316</t>
+          <t>166754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180250</t>
+          <t>180721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163495</t>
+          <t>164260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180522</t>
+          <t>181371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>335925</t>
+          <t>334599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357394</t>
+          <t>356565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116961</t>
+          <t>116903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149439</t>
+          <t>151293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143277</t>
+          <t>143533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179505</t>
+          <t>179665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271234</t>
+          <t>272281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317509</t>
+          <t>320747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>531582</t>
+          <t>529728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>564060</t>
+          <t>564118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543195</t>
+          <t>543035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579423</t>
+          <t>579167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1086212</t>
+          <t>1082974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1132487</t>
+          <t>1131440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>51639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>70321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48492</t>
+          <t>48963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67836</t>
+          <t>68100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104898</t>
+          <t>105250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132791</t>
+          <t>133365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76221</t>
+          <t>76440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96634</t>
+          <t>95122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78154</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97498</t>
+          <t>97027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159960</t>
+          <t>159386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>187501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44738</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66966</t>
+          <t>65674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54963</t>
+          <t>56652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78516</t>
+          <t>78768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108045</t>
+          <t>105508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140057</t>
+          <t>137754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168521</t>
+          <t>169813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190749</t>
+          <t>191276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189802</t>
+          <t>189550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213355</t>
+          <t>211666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363748</t>
+          <t>366051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>395760</t>
+          <t>398297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>20287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>27354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59584</t>
+          <t>57842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120462</t>
+          <t>120655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136072</t>
+          <t>136081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129721</t>
+          <t>130592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144273</t>
+          <t>144006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254730</t>
+          <t>256472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276655</t>
+          <t>278047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18285</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33779</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>57597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143048</t>
+          <t>142415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157007</t>
+          <t>157039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145176</t>
+          <t>145626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160670</t>
+          <t>159890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292828</t>
+          <t>292695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313469</t>
+          <t>313212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>145285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180809</t>
+          <t>183629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151924</t>
+          <t>151532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189534</t>
+          <t>188742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307151</t>
+          <t>307721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>360128</t>
+          <t>361743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529144</t>
+          <t>526324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>564433</t>
+          <t>564668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561675</t>
+          <t>562467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>599285</t>
+          <t>599677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1101034</t>
+          <t>1099419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1154011</t>
+          <t>1153441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35158</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>53012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>34414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>51118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75001</t>
+          <t>74966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99541</t>
+          <t>98816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78887</t>
+          <t>78642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96496</t>
+          <t>95415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71487</t>
+          <t>72396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>89100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155627</t>
+          <t>156352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180167</t>
+          <t>180202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>51467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38970</t>
+          <t>39147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59833</t>
+          <t>59569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79747</t>
+          <t>79663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106725</t>
+          <t>106249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157847</t>
+          <t>159050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176043</t>
+          <t>176608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197644</t>
+          <t>197908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218507</t>
+          <t>218330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361269</t>
+          <t>361745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>388247</t>
+          <t>388331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>25330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>43970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>56726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82719</t>
+          <t>81255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146154</t>
+          <t>145454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163909</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142070</t>
+          <t>142562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159443</t>
+          <t>159854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>292107</t>
+          <t>293571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317440</t>
+          <t>318100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>32019</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53062</t>
+          <t>53548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140656</t>
+          <t>140586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155363</t>
+          <t>155622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146245</t>
+          <t>146655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160713</t>
+          <t>160651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292877</t>
+          <t>292391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313690</t>
+          <t>312727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128350</t>
+          <t>127645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163278</t>
+          <t>161928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>129843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164987</t>
+          <t>164378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264740</t>
+          <t>266751</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313988</t>
+          <t>316631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>539792</t>
+          <t>541142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>574720</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>575870</t>
+          <t>576479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>611451</t>
+          <t>611014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129939</t>
+          <t>1127296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1179187</t>
+          <t>1177176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43138</t>
+          <t>42241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37178</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47862</t>
+          <t>47940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75817</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90728</t>
+          <t>90608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>20977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37692</t>
+          <t>37554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25476</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>43005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50628</t>
+          <t>51473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74758</t>
+          <t>74910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121607</t>
+          <t>121745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137846</t>
+          <t>138322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138458</t>
+          <t>139549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157078</t>
+          <t>156789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267095</t>
+          <t>266943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291225</t>
+          <t>290380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>42724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48259</t>
+          <t>47498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55444</t>
+          <t>55135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85362</t>
+          <t>83433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130063</t>
+          <t>130348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150261</t>
+          <t>149955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164231</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185026</t>
+          <t>185097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>300201</t>
+          <t>302130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330119</t>
+          <t>330428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34354</t>
+          <t>34495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31487</t>
+          <t>32363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56161</t>
+          <t>57038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54767</t>
+          <t>53147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84217</t>
+          <t>82403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241104</t>
+          <t>240963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259042</t>
+          <t>259652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249322</t>
+          <t>248445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273996</t>
+          <t>273120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>496723</t>
+          <t>498537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>526173</t>
+          <t>527793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83926</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>116826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113277</t>
+          <t>113296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>151520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206386</t>
+          <t>207822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259768</t>
+          <t>258123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544742</t>
+          <t>548514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>581414</t>
+          <t>583260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>612244</t>
+          <t>610452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>648695</t>
+          <t>648676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1167544</t>
+          <t>1169189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220926</t>
+          <t>1219490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP17-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40141</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32253</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48888</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>43745</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>35161</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51043</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36086</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51896</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40141</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>32564</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48263</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72605</t>
+          <t>71935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94637</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81239</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>72492</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89127</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>62426</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55128</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71010</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54275</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70085</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>58,8%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>51,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>81239</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>88816</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132914</t>
+          <t>131505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154946</t>
+          <t>155616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61062</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50924</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72354</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>49802</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39441</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60535</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>40922</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61539</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61062</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>50392</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72588</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96017</t>
+          <t>96095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>127056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>192694</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>181402</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>202832</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203403</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>192670</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>213764</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191666</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>212283</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>192694</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>181168</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>203364</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380768</t>
+          <t>379905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410944</t>
+          <t>410866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27442</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19904</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35871</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19738</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14441</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27693</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13817</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26626</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27442</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20815</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>35289</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37269</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57180</t>
+          <t>57409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114073</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105644</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>121611</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>107810</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>99855</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>113107</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>100922</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>113731</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>114073</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>106226</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>120700</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211883</t>
+          <t>211654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231794</t>
+          <t>231103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33191</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25637</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42764</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20302</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13376</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27343</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14310</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28644</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33191</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24678</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>41789</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>43036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65547</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172858</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163285</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180412</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173795</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>166754</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180721</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>165453</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>179787</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172858</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>164260</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>181371</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>334599</t>
+          <t>335437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>356565</t>
+          <t>357110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>144249</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>180387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>133587</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>116903</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>151293</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>118374</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>150599</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>161836</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>143533</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>179665</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272281</t>
+          <t>272305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320747</t>
+          <t>320612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>560864</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>542313</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>578451</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>77,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>817</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>547434</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>529728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>564118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>530422</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>562647</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>77,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>560864</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>543035</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>579167</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>77,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1082974</t>
+          <t>1083109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1131440</t>
+          <t>1131416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2012 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58112</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48406</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68055</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>60262</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51639</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70321</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>50429</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>69886</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,06%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>58112</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>48963</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>68100</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105250</t>
+          <t>105101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133365</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>87878</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77935</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97584</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>66,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>86499</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>76440</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>95122</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>76875</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>96332</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>58,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>87878</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>77890</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97027</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>60,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159386</t>
+          <t>161843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187501</t>
+          <t>187650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67207</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56346</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>81213</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54949</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44211</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65674</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44075</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>66782</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67207</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>56652</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>78768</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105508</t>
+          <t>106477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137754</t>
+          <t>139633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>201111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>187105</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>211972</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>74,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>180538</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>169813</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>191276</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>168705</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191412</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>76,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>201111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>189550</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>211666</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366051</t>
+          <t>364172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398297</t>
+          <t>397328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268318</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268318</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268318</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>235487</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>235487</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>235487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268318</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268318</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268318</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19852</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13468</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27177</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>26967</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20287</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35713</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20017</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35331</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19852</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13940</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27354</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57842</t>
+          <t>57412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138094</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130769</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>144478</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>129401</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120655</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>136081</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>121037</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>136351</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>138094</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>130592</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>144006</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>256472</t>
+          <t>256902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278047</t>
+          <t>277094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157946</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157946</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157946</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157946</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157946</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157946</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25410</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18624</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33134</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20967</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14298</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28922</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14484</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29066</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25410</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19065</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33329</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37080</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>58100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>153545</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160331</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>150370</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>142415</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>157039</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>142271</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>156853</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>153545</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>145626</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>159890</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292695</t>
+          <t>292192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313212</t>
+          <t>313408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>178955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>178955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>178955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>151559</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>189799</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>163145</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>145285</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>183629</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>143342</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>180478</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>151532</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>188742</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307721</t>
+          <t>307512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361743</t>
+          <t>360492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>580628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>561410</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>599650</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>77,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>546808</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>526324</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>564668</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>529475</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>566611</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>77,02%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>580628</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>562467</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>599677</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1099419</t>
+          <t>1100670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1153441</t>
+          <t>1153650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>751209</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>751209</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>751209</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709953</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709953</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709953</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>751209</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>751209</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>751209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2016 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34961</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51917</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>44437</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36239</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53012</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36044</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53214</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>34414</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51118</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74966</t>
+          <t>75778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98816</t>
+          <t>98712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80827</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71597</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87217</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>78642</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>95415</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>78440</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>95610</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>66,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80827</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>72396</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>89100</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>65,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156352</t>
+          <t>156456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180202</t>
+          <t>179390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>123514</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>123514</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>123514</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>123514</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>123514</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>123514</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48947</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39459</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>59926</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>43195</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33909</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>51467</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>34774</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>53095</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48947</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39147</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>59569</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,01%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79663</t>
+          <t>78487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106249</t>
+          <t>106217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>208530</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>197551</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>218018</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>167322</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159050</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>176608</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>157422</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>175743</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>208530</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>197908</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>218330</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,99%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361745</t>
+          <t>361777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>388331</t>
+          <t>389507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257477</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257477</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257477</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257477</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257477</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257477</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35739</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27220</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45546</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32733</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25330</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42840</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25109</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42964</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35739</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>26678</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>43970</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56726</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81255</t>
+          <t>80555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>150793</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140986</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159312</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155561</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>145454</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>162964</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>145330</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>163185</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>150793</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142562</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>159854</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,84%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293571</t>
+          <t>294271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318100</t>
+          <t>318645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,01%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186532</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186532</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186532</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188294</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188294</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188294</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186532</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186532</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186532</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18746</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12511</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26453</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>23521</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16983</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32019</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17239</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31952</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18746</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12683</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26679</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53548</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>154588</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>146881</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160823</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>149084</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140586</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>155622</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>140653</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>155366</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>154588</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>146655</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>160651</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,19%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292391</t>
+          <t>293334</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312727</t>
+          <t>313071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173334</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173334</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173334</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172605</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172605</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172605</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173334</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173334</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173334</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>127328</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>163833</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>143886</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>127645</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>161928</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>126750</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>161597</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>146119</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>129843</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>164378</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>266751</t>
+          <t>266309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316631</t>
+          <t>314781</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>594738</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>577024</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>613529</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>836</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>559184</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>541142</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>575425</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>541473</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>576320</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>594738</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>576479</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>611014</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1127296</t>
+          <t>1129146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1177176</t>
+          <t>1177618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -6220,52 +6220,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>703070</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703070</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703070</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11220</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19969</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11560</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21816</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24626</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28347</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42241</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35185</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30568</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39317</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41216</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35695</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45951</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42997</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36818</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47940</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>84213</t>
+          <t>72208</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76714</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90608</t>
+          <t>78463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37536</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20977</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37554</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51473</t>
+          <t>45567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74910</t>
+          <t>65224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>128376</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>119986</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>135481</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>131101</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>121745</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>138322</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>148826</t>
+          <t>120118</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>139549</t>
+          <t>112460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>156789</t>
+          <t>127188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>279928</t>
+          <t>248493</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>266943</t>
+          <t>237815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290380</t>
+          <t>257472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25970</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45803</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23117</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42724</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47498</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83433</t>
+          <t>77589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164563</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154323</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>174156</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>141776</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130348</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149955</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>81,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>175619</t>
+          <t>145118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164992</t>
+          <t>135806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185097</t>
+          <t>153557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>317396</t>
+          <t>309681</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302130</t>
+          <t>297209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330428</t>
+          <t>322438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30658</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54410</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15806</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34495</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,9%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32363</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57038</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53147</t>
+          <t>53667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82403</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>250985</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>238235</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>261987</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>250932</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>240963</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>259652</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,1%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>262937</t>
+          <t>231063</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>248445</t>
+          <t>221987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273120</t>
+          <t>238641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>513869</t>
+          <t>482048</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>498537</t>
+          <t>467391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527793</t>
+          <t>495531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>105312</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>138293</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>82080</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>116826</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113296</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151520</t>
+          <t>111378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207822</t>
+          <t>195795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258123</t>
+          <t>241364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>565026</t>
+          <t>579107</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>548514</t>
+          <t>562536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>583260</t>
+          <t>595517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>630380</t>
+          <t>533321</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>610452</t>
+          <t>517455</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>648676</t>
+          <t>547069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1195406</t>
+          <t>1112428</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1169189</t>
+          <t>1088298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1219490</t>
+          <t>1133867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
